--- a/informes_data/Primera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_MOVISTAR ESTUDIANTES.xlsx
+++ b/informes_data/Primera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_MOVISTAR ESTUDIANTES.xlsx
@@ -565,13 +565,13 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>16.0247</v>
+        <v>17.5716</v>
       </c>
       <c r="E2" t="n">
-        <v>14.4699</v>
+        <v>15.7166</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5547</v>
+        <v>1.8551</v>
       </c>
       <c r="G2" t="n">
         <v>16.0068</v>
@@ -610,13 +610,13 @@
         <v>4.846</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1804</v>
+        <v>1.3666</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4516000000000001</v>
+        <v>0.7949999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2712</v>
+        <v>0.5715</v>
       </c>
       <c r="V2" t="n">
         <v>-1.1234</v>
@@ -643,13 +643,13 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>8.1808</v>
+        <v>10.295</v>
       </c>
       <c r="E3" t="n">
-        <v>4.6522</v>
+        <v>6.367599999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>3.5286</v>
+        <v>3.9275</v>
       </c>
       <c r="G3" t="n">
         <v>5.303599999999999</v>
@@ -688,13 +688,13 @@
         <v>5.0663</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6234000000000001</v>
+        <v>1.4908</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.8811</v>
+        <v>-0.1659000000000002</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2577</v>
+        <v>1.6566</v>
       </c>
       <c r="V3" t="n">
         <v>0.6369999999999999</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. NWOGBO</t>
+          <t>J. GRANGER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>7.84</v>
+        <v>7.4337</v>
       </c>
       <c r="E4" t="n">
-        <v>4.5047</v>
+        <v>4.788799999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>3.3353</v>
+        <v>2.6449</v>
       </c>
       <c r="G4" t="n">
-        <v>2.3472</v>
+        <v>7.092099999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>1.5305</v>
+        <v>0.5060000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8167</v>
+        <v>6.586099999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>1.493</v>
+        <v>10.0086</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6956000000000003</v>
+        <v>-0.6245999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7974</v>
+        <v>10.6334</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8541</v>
+        <v>-2.9166</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8349</v>
+        <v>1.1306</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01930000000000004</v>
+        <v>-4.0472</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3216</v>
+        <v>-3.3041</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.2028</v>
+        <v>-7.7095</v>
       </c>
       <c r="R4" t="n">
-        <v>3.5244</v>
+        <v>4.4054</v>
       </c>
       <c r="S4" t="n">
-        <v>2.2347</v>
+        <v>0.4053999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3027</v>
+        <v>-0.8625999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9320999999999999</v>
+        <v>1.268</v>
       </c>
       <c r="V4" t="n">
-        <v>1.9365</v>
+        <v>3.2404</v>
       </c>
       <c r="W4" t="n">
-        <v>3.9117</v>
+        <v>3.3523</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.9752</v>
+        <v>-0.1119</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T. MC GREW</t>
+          <t>L. NWOGBO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>6.1678</v>
+        <v>7.1991</v>
       </c>
       <c r="E5" t="n">
-        <v>4.0207</v>
+        <v>3.6955</v>
       </c>
       <c r="F5" t="n">
-        <v>2.1471</v>
+        <v>3.5036</v>
       </c>
       <c r="G5" t="n">
-        <v>5.0512</v>
+        <v>2.3472</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8059999999999998</v>
+        <v>1.5305</v>
       </c>
       <c r="I5" t="n">
-        <v>4.2453</v>
+        <v>0.8167</v>
       </c>
       <c r="J5" t="n">
-        <v>6.8654</v>
+        <v>1.493</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002999999999999961</v>
+        <v>0.6956000000000003</v>
       </c>
       <c r="L5" t="n">
-        <v>6.862500000000001</v>
+        <v>0.7974</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.8142</v>
+        <v>0.8541</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8029999999999999</v>
+        <v>0.8349</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.6172</v>
+        <v>0.01930000000000004</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5419</v>
+        <v>1.3216</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.3041</v>
+        <v>-2.2028</v>
       </c>
       <c r="R5" t="n">
-        <v>4.846</v>
+        <v>3.5244</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8784999999999999</v>
+        <v>1.5938</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6595</v>
+        <v>0.4935</v>
       </c>
       <c r="U5" t="n">
-        <v>1.538</v>
+        <v>1.1003</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.3039</v>
+        <v>1.9365</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1189</v>
+        <v>3.9117</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.4228</v>
+        <v>-1.9752</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. GRANGER</t>
+          <t>T. MC GREW</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>5.824399999999999</v>
+        <v>6.678800000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>4.0108</v>
+        <v>4.277</v>
       </c>
       <c r="F6" t="n">
-        <v>1.8136</v>
+        <v>2.4018</v>
       </c>
       <c r="G6" t="n">
-        <v>7.092099999999999</v>
+        <v>5.0512</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5060000000000001</v>
+        <v>0.8059999999999998</v>
       </c>
       <c r="I6" t="n">
-        <v>6.586099999999999</v>
+        <v>4.2453</v>
       </c>
       <c r="J6" t="n">
-        <v>10.0086</v>
+        <v>6.8654</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6245999999999999</v>
+        <v>0.002999999999999961</v>
       </c>
       <c r="L6" t="n">
-        <v>10.6334</v>
+        <v>6.862500000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.9166</v>
+        <v>-1.8142</v>
       </c>
       <c r="N6" t="n">
-        <v>1.1306</v>
+        <v>0.8029999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>-4.0472</v>
+        <v>-2.6172</v>
       </c>
       <c r="P6" t="n">
+        <v>1.5419</v>
+      </c>
+      <c r="Q6" t="n">
         <v>-3.3041</v>
       </c>
-      <c r="Q6" t="n">
-        <v>-7.7095</v>
-      </c>
       <c r="R6" t="n">
-        <v>4.4054</v>
+        <v>4.846</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.2038</v>
+        <v>1.3896</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.6406</v>
+        <v>-0.4033</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4367</v>
+        <v>1.7929</v>
       </c>
       <c r="V6" t="n">
-        <v>3.2404</v>
+        <v>-1.3039</v>
       </c>
       <c r="W6" t="n">
-        <v>3.3523</v>
+        <v>1.1189</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1119</v>
+        <v>-2.4228</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>4.3698</v>
+        <v>5.2976</v>
       </c>
       <c r="E7" t="n">
-        <v>1.7875</v>
+        <v>2.5014</v>
       </c>
       <c r="F7" t="n">
-        <v>2.5824</v>
+        <v>2.7962</v>
       </c>
       <c r="G7" t="n">
         <v>2.5241</v>
@@ -1000,13 +1000,13 @@
         <v>2.6432</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.01779999999999998</v>
+        <v>0.9099999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9203</v>
+        <v>-0.2064</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9025000000000001</v>
+        <v>1.1164</v>
       </c>
       <c r="V7" t="n">
         <v>-0.5595</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. NIANG</t>
+          <t>P. GARINO GULLOTTA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>3.7201</v>
+        <v>3.9731</v>
       </c>
       <c r="E8" t="n">
-        <v>3.8745</v>
+        <v>2.9449</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1544</v>
+        <v>1.0282</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1405000000000001</v>
+        <v>0.2995999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>3.058</v>
+        <v>0.3539999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.9177</v>
+        <v>-0.0544</v>
       </c>
       <c r="J8" t="n">
-        <v>4.1836</v>
+        <v>1.3714</v>
       </c>
       <c r="K8" t="n">
-        <v>3.614</v>
+        <v>-1.5039</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5696</v>
+        <v>2.8754</v>
       </c>
       <c r="M8" t="n">
-        <v>-4.0431</v>
+        <v>-1.0718</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5558999999999999</v>
+        <v>1.8579</v>
       </c>
       <c r="O8" t="n">
-        <v>-3.4872</v>
+        <v>-2.9297</v>
       </c>
       <c r="P8" t="n">
-        <v>1.542</v>
+        <v>3.7446</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1014</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.6433</v>
+        <v>3.7446</v>
       </c>
       <c r="S8" t="n">
-        <v>3.1567</v>
+        <v>1.1596</v>
       </c>
       <c r="T8" t="n">
-        <v>1.1667</v>
+        <v>-0.1049</v>
       </c>
       <c r="U8" t="n">
-        <v>1.99</v>
+        <v>1.2644</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.1189</v>
+        <v>-1.2309</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.3745</v>
+        <v>1.6784</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.7444999999999999</v>
+        <v>-2.9092</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. GARINO GULLOTTA</t>
+          <t>S. SALIN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>2.507</v>
+        <v>3.1111</v>
       </c>
       <c r="E9" t="n">
-        <v>2.4544</v>
+        <v>0.2797999999999998</v>
       </c>
       <c r="F9" t="n">
-        <v>0.05270000000000008</v>
+        <v>2.8312</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2995999999999999</v>
+        <v>-0.9075000000000002</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3539999999999999</v>
+        <v>-0.6748</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0544</v>
+        <v>-0.2327000000000004</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3714</v>
+        <v>0.3062999999999998</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.5039</v>
+        <v>0.647</v>
       </c>
       <c r="L9" t="n">
-        <v>2.8754</v>
+        <v>-0.3407999999999998</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.0718</v>
+        <v>-1.2138</v>
       </c>
       <c r="N9" t="n">
-        <v>1.8579</v>
+        <v>-1.3218</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.9297</v>
+        <v>0.1082</v>
       </c>
       <c r="P9" t="n">
-        <v>3.7446</v>
+        <v>2.423</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.3217</v>
       </c>
       <c r="R9" t="n">
-        <v>3.7446</v>
+        <v>3.7447</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3063</v>
+        <v>1.2166</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5953999999999999</v>
+        <v>0.1764</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2891</v>
+        <v>1.0403</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2309</v>
+        <v>0.379</v>
       </c>
       <c r="W9" t="n">
-        <v>1.6784</v>
+        <v>1.1189</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.9092</v>
+        <v>-0.7399</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. SALIN</t>
+          <t>M. NIANG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>2.267</v>
+        <v>1.9932</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2637999999999998</v>
+        <v>2.5966</v>
       </c>
       <c r="F10" t="n">
-        <v>2.5309</v>
+        <v>-0.6032999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.9075000000000002</v>
+        <v>0.1405000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6748</v>
+        <v>3.058</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2327000000000004</v>
+        <v>-2.9177</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3062999999999998</v>
+        <v>4.1836</v>
       </c>
       <c r="K10" t="n">
-        <v>0.647</v>
+        <v>3.614</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.3407999999999998</v>
+        <v>0.5696</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.2138</v>
+        <v>-4.0431</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.3218</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1082</v>
+        <v>-3.4872</v>
       </c>
       <c r="P10" t="n">
-        <v>2.423</v>
+        <v>1.542</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.3217</v>
+        <v>-1.1014</v>
       </c>
       <c r="R10" t="n">
-        <v>3.7447</v>
+        <v>2.6433</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3726</v>
+        <v>1.4299</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3674</v>
+        <v>-0.1112</v>
       </c>
       <c r="U10" t="n">
-        <v>0.74</v>
+        <v>1.5409</v>
       </c>
       <c r="V10" t="n">
-        <v>0.379</v>
+        <v>-1.1189</v>
       </c>
       <c r="W10" t="n">
-        <v>1.1189</v>
+        <v>-0.3745</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.7399</v>
+        <v>-0.7444999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. STUMBRIS</t>
+          <t>A. GONZALEZ PEREZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1.7899</v>
+        <v>1.6362</v>
       </c>
       <c r="E11" t="n">
-        <v>3.1796</v>
+        <v>0.0877</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3897</v>
+        <v>1.5486</v>
       </c>
       <c r="G11" t="n">
-        <v>1.2585</v>
+        <v>1.2339</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3828</v>
+        <v>0.5668</v>
       </c>
       <c r="I11" t="n">
-        <v>1.6415</v>
+        <v>0.6672</v>
       </c>
       <c r="J11" t="n">
-        <v>3.5828</v>
+        <v>0.3018</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8214</v>
+        <v>0.0359</v>
       </c>
       <c r="L11" t="n">
-        <v>2.7615</v>
+        <v>0.2658</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.3242</v>
+        <v>0.9322</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.2044</v>
+        <v>0.5308</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.1199</v>
+        <v>0.4014</v>
       </c>
       <c r="P11" t="n">
-        <v>0.8810000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2028</v>
+        <v>-0.2203</v>
       </c>
       <c r="R11" t="n">
-        <v>3.0838</v>
+        <v>0.2203</v>
       </c>
       <c r="S11" t="n">
-        <v>2.7443</v>
+        <v>0.4023</v>
       </c>
       <c r="T11" t="n">
-        <v>1.7994</v>
+        <v>0.0062</v>
       </c>
       <c r="U11" t="n">
-        <v>0.9450000000000001</v>
+        <v>0.3961</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.0942</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.0942</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. GONZALEZ PEREZ</t>
+          <t>R. STUMBRIS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>1.6902</v>
+        <v>0.8198000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1466</v>
+        <v>2.3704</v>
       </c>
       <c r="F12" t="n">
-        <v>1.8368</v>
+        <v>-1.5506</v>
       </c>
       <c r="G12" t="n">
-        <v>1.2339</v>
+        <v>1.2585</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5668</v>
+        <v>-0.3828</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6672</v>
+        <v>1.6415</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3018</v>
+        <v>3.5828</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0359</v>
+        <v>0.8214</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2658</v>
+        <v>2.7615</v>
       </c>
       <c r="M12" t="n">
-        <v>0.9322</v>
+        <v>-2.3242</v>
       </c>
       <c r="N12" t="n">
-        <v>0.5308</v>
+        <v>-1.2044</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4014</v>
+        <v>-1.1199</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>0.8810000000000001</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.2203</v>
+        <v>-2.2028</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2203</v>
+        <v>3.0838</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4562</v>
+        <v>1.7743</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2281</v>
+        <v>0.9903</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6843</v>
+        <v>0.7841</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-3.0942</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-3.0942</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>H. LOPEZ BARRANTES</t>
+          <t>A. GONZÁLEZ PÉREZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.5153</v>
+        <v>0.2696</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9004000000000001</v>
+        <v>0.2696</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6149</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.262</v>
+        <v>0.2696</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.9258</v>
+        <v>0.2696</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6637</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.2448</v>
+        <v>0.2696</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.7765</v>
+        <v>0.2696</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5316000000000001</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.01729999999999998</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1494</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1322</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0.6608000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.3217</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.9824</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.0415</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.3478</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6936</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.9249999999999999</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.1189</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.0439</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. GONZÁLEZ PÉREZ</t>
+          <t>H. LOPEZ BARRANTES</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2696</v>
+        <v>0.1529</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2696</v>
+        <v>-0.2603000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>0.4132</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2696</v>
+        <v>-1.262</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2696</v>
+        <v>-1.9258</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>0.6637</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2696</v>
+        <v>-1.2448</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2696</v>
+        <v>-1.7765</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>0.5316000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>-0.01729999999999998</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>-0.1494</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>0.1322</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>0.6608000000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-1.3217</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.9824</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.6789</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.1871</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>0.4919</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>-0.9249999999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.1189</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-2.0439</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>62.1666</v>
+        <v>66.43169999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>43.71389999999999</v>
+        <v>45.6356</v>
       </c>
       <c r="F15" t="n">
-        <v>18.4529</v>
+        <v>20.7964</v>
       </c>
       <c r="G15" t="n">
         <v>39.35759999999999</v>
@@ -1597,19 +1597,19 @@
         <v>27.4821</v>
       </c>
       <c r="J15" t="n">
-        <v>55.389</v>
+        <v>55.38899999999999</v>
       </c>
       <c r="K15" t="n">
         <v>11.2276</v>
       </c>
       <c r="L15" t="n">
-        <v>44.16159999999999</v>
+        <v>44.1616</v>
       </c>
       <c r="M15" t="n">
         <v>-16.0314</v>
       </c>
       <c r="N15" t="n">
-        <v>0.6479000000000005</v>
+        <v>0.6479000000000006</v>
       </c>
       <c r="O15" t="n">
         <v>-16.6789</v>
@@ -1621,16 +1621,16 @@
         <v>-25.3317</v>
       </c>
       <c r="R15" t="n">
-        <v>40.75040000000001</v>
+        <v>40.7504</v>
       </c>
       <c r="S15" t="n">
-        <v>10.5528</v>
+        <v>14.8178</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1273999999999997</v>
+        <v>1.7942</v>
       </c>
       <c r="U15" t="n">
-        <v>10.6802</v>
+        <v>13.0234</v>
       </c>
       <c r="V15" t="n">
         <v>-3.1629</v>
